--- a/assets/constructions/examples/ctd_tsmb_holdersquare.xlsx
+++ b/assets/constructions/examples/ctd_tsmb_holdersquare.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE6"/>
+  <dimension ref="A1:AI6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -584,11 +584,31 @@
           <t>releasepack</t>
         </is>
       </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MHD1212-6L1000</t>
+          <t>MHS0625-7</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -598,39 +618,43 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Microscope</t>
+          <t>Microscope Holders</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E2" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="n">
+        <v>15.875</v>
+      </c>
       <c r="L2" t="n">
-        <v>18</v>
+        <v>15.875</v>
       </c>
       <c r="M2" t="n">
-        <v>12</v>
+        <v>15.875</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
+      <c r="P2" t="n">
+        <v>26.492</v>
+      </c>
       <c r="Q2" t="n">
-        <v>99</v>
+        <v>127</v>
       </c>
       <c r="R2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr">
@@ -639,22 +663,22 @@
         </is>
       </c>
       <c r="U2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr">
         <is>
-          <t>ISO_5610:12X12</t>
+          <t>ISO_5610:15.875X15.875</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>VARGUS_D:6</t>
+          <t>VARGUS_D:7</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>VAR_MICR:6</t>
+          <t>VAR_MICR:7</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
@@ -667,19 +691,31 @@
       </c>
       <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>2019 / Groovex Catalog</t>
-        </is>
+          <t>2019 / Groovex Catalog Inch</t>
+        </is>
+      </c>
+      <c r="AF2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>191.95</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AI2" t="n">
+        <v>17646.67</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MHD0500-4L0700</t>
+          <t>MHS1212-5</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -693,39 +729,43 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E3" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="n">
+        <v>12</v>
+      </c>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="n">
+        <v>12</v>
+      </c>
       <c r="L3" t="n">
-        <v>12.7</v>
+        <v>12</v>
       </c>
       <c r="M3" t="n">
-        <v>12.7</v>
+        <v>12</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="n">
-        <v>36.5</v>
+        <v>12</v>
       </c>
       <c r="P3" t="n">
-        <v>18.999</v>
+        <v>21.5</v>
       </c>
       <c r="Q3" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="R3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr">
@@ -734,22 +774,22 @@
         </is>
       </c>
       <c r="U3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr">
         <is>
-          <t>ISO_5610:12.7X12.7</t>
+          <t>ISO_5610:12X12</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>VARGUS_D:4</t>
+          <t>VARGUS_D:5</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>VAR_MICR:4</t>
+          <t>VAR_MICR:5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -762,17 +802,33 @@
       </c>
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="inlineStr"/>
+      <c r="AD3" t="n">
+        <v>0</v>
+      </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>2019 / Groovex Catalog Inch</t>
-        </is>
+          <t>2019 / Groovex Catalog</t>
+        </is>
+      </c>
+      <c r="AF3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>191.95</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AI3" t="n">
+        <v>17646.67</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>MHD0375-6L0800</t>
+          <t>MHS0625-4</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -782,43 +838,43 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Microscope</t>
+          <t>Microscope Holders</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="n">
+        <v>15.875</v>
+      </c>
       <c r="L4" t="n">
-        <v>9.525</v>
+        <v>15.875</v>
       </c>
       <c r="M4" t="n">
-        <v>9.525</v>
+        <v>15.875</v>
       </c>
       <c r="N4" t="inlineStr"/>
-      <c r="O4" t="n">
-        <v>53.01</v>
-      </c>
+      <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
-        <v>16.002</v>
+        <v>24.994</v>
       </c>
       <c r="Q4" t="n">
-        <v>99</v>
+        <v>127</v>
       </c>
       <c r="R4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr">
@@ -827,22 +883,22 @@
         </is>
       </c>
       <c r="U4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr">
         <is>
-          <t>ISO_5610:9.525X9.525</t>
+          <t>ISO_5610:15.875X15.875</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>VARGUS_D:6</t>
+          <t>VARGUS_D:4</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>VAR_MICR:6</t>
+          <t>VAR_MICR:4</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -861,11 +917,25 @@
           <t>2019 / Groovex Catalog Inch</t>
         </is>
       </c>
+      <c r="AF4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>191.95</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AI4" t="n">
+        <v>17646.67</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MHD0375-5L0800</t>
+          <t>MHD1212-4L0700</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -879,7 +949,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E5" t="n">
         <v>90</v>
@@ -895,18 +965,14 @@
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
-        <v>9.525</v>
+        <v>18</v>
       </c>
       <c r="M5" t="n">
-        <v>9.525</v>
+        <v>12</v>
       </c>
       <c r="N5" t="inlineStr"/>
-      <c r="O5" t="n">
-        <v>48</v>
-      </c>
-      <c r="P5" t="n">
-        <v>16.002</v>
-      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
       <c r="Q5" t="n">
         <v>99</v>
       </c>
@@ -925,17 +991,17 @@
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr">
         <is>
-          <t>ISO_5610:9.525X9.525</t>
+          <t>ISO_5610:12X12</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>VARGUS_D:5</t>
+          <t>VARGUS_D:4</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>VAR_MICR:5</t>
+          <t>VAR_MICR:4</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -948,17 +1014,33 @@
       </c>
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr"/>
-      <c r="AD5" t="inlineStr"/>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>2019 / Groovex Catalog Inch</t>
-        </is>
+          <t>2019 / Groovex Catalog</t>
+        </is>
+      </c>
+      <c r="AF5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>397.93</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AI5" t="n">
+        <v>36583.18</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MHS1010-4</t>
+          <t>MHS0625-6</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -968,11 +1050,11 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Microscope</t>
+          <t>Microscope Holders</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -981,31 +1063,27 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="H6" t="inlineStr"/>
-      <c r="I6" t="n">
-        <v>10</v>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="n">
-        <v>10</v>
+        <v>15.875</v>
       </c>
       <c r="L6" t="n">
-        <v>10</v>
+        <v>15.875</v>
       </c>
       <c r="M6" t="n">
-        <v>10</v>
+        <v>15.875</v>
       </c>
       <c r="N6" t="inlineStr"/>
-      <c r="O6" t="n">
-        <v>10</v>
-      </c>
+      <c r="O6" t="inlineStr"/>
       <c r="P6" t="n">
-        <v>19</v>
+        <v>26.01</v>
       </c>
       <c r="Q6" t="n">
-        <v>100</v>
+        <v>127</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1022,17 +1100,17 @@
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr">
         <is>
-          <t>ISO_5610:10X10</t>
+          <t>ISO_5610:15.875X15.875</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>VARGUS_D:4</t>
+          <t>VARGUS_D:6</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>VAR_MICR:4</t>
+          <t>VAR_MICR:6</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1045,13 +1123,25 @@
       </c>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>2019 / Groovex Catalog</t>
-        </is>
+          <t>2019 / Groovex Catalog Inch</t>
+        </is>
+      </c>
+      <c r="AF6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>191.95</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AI6" t="n">
+        <v>17646.67</v>
       </c>
     </row>
   </sheetData>
